--- a/erp-server/erp-server-file/src/main/resources/excel/plm/productForbiddenWord.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/productForbiddenWord.xlsx
@@ -12,6 +12,23 @@
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t>{.forbiddenWord}</t>
+  </si>
+  <si>
+    <t>{.disabledName}</t>
+  </si>
+  <si>
+    <t>{.createUserName}</t>
+  </si>
+  <si>
+    <t>{.createTime}</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -439,25 +456,17 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>{.forbiddenWord}</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>{.disabledName}</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>{.createUserName}</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>{.createTime}</t>
-        </is>
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
